--- a/scripts/autogenerated_parts/autogenerated_parts.xlsx
+++ b/scripts/autogenerated_parts/autogenerated_parts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dan\Documents\Projects\P0002_KicadWorkflow\libraries\P0002-LIB-001_KicadComponentLibrary\scripts\autogenerated_parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{073F18B7-1DA6-4CC9-BFF5-44B5030AE147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DDF676-A33C-4DE0-AF9F-304D4D8A8246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="34500" windowHeight="13560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="23232" windowHeight="18576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="capacitor" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17506" uniqueCount="2314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17543" uniqueCount="2325">
   <si>
     <t>Manufacturer</t>
   </si>
@@ -6985,6 +6985,39 @@
   </si>
   <si>
     <t>Capacitor_WUT:C_0402_1005Metric</t>
+  </si>
+  <si>
+    <t>12k4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RK73H1ETTP1242F </t>
+  </si>
+  <si>
+    <t>0603L050SL</t>
+  </si>
+  <si>
+    <t>https://www.littelfuse.com/assetdocs/resettable-ptcs-low-rho-smd-ptc-datasheet?assetguid=b786faf0-de16-4763-9d22-6b8080943caf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hongjiacheng </t>
+  </si>
+  <si>
+    <t>H5VND5U</t>
+  </si>
+  <si>
+    <t>5V</t>
+  </si>
+  <si>
+    <t>https://jlcpcb.com/partdetail/hongjiacheng-H5VND5U/C42413865</t>
+  </si>
+  <si>
+    <t>GRM21BR61A476ME15</t>
+  </si>
+  <si>
+    <t>Capacitor_SMD:C_0805_2012Metric</t>
+  </si>
+  <si>
+    <t>https://pim.murata.com/en-eu/pim/details/?partNum=GRM21BR61A476ME15L</t>
   </si>
 </sst>
 </file>
@@ -7331,7 +7364,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{843D31F6-53B3-4092-975A-990A26A0450A}">
-  <dimension ref="A1:L1160"/>
+  <dimension ref="A1:L1161"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -49772,6 +49805,41 @@
         <v>118</v>
       </c>
       <c r="L1160" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B1161" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C1161" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D1161" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E1161" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="F1161" t="s">
+        <v>2323</v>
+      </c>
+      <c r="G1161" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="H1161" s="8" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I1161" t="s">
+        <v>2324</v>
+      </c>
+      <c r="J1161" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="K1161" t="s">
+        <v>60</v>
+      </c>
+      <c r="L1161" t="s">
         <v>43</v>
       </c>
     </row>
@@ -49791,7 +49859,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DB8545-37D6-4E42-AAF5-E598132F76B8}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -50983,6 +51051,35 @@
         <v>1717</v>
       </c>
       <c r="I41" s="1" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>2320</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H42" t="s">
+        <v>2321</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>1707</v>
       </c>
     </row>
@@ -51459,7 +51556,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78DDF41A-55F4-4F50-85C1-C107668A0205}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -51633,6 +51730,35 @@
         <v>1683</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>1682</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2317</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>1685</v>
       </c>
     </row>
@@ -52273,7 +52399,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F54A169-EC5A-4D55-91FC-C8FC35931905}">
-  <dimension ref="A1:J514"/>
+  <dimension ref="A1:J515"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -68722,6 +68848,38 @@
       </c>
       <c r="J514">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A515" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B515" t="s">
+        <v>2315</v>
+      </c>
+      <c r="C515" s="1" t="s">
+        <v>2314</v>
+      </c>
+      <c r="D515" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E515" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F515" s="1" t="s">
+        <v>2312</v>
+      </c>
+      <c r="G515" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H515" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="I515" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="J515">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/autogenerated_parts/autogenerated_parts.xlsx
+++ b/scripts/autogenerated_parts/autogenerated_parts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dan\Documents\Projects\P0002_KicadWorkflow\libraries\P0002-LIB-001_KicadComponentLibrary\scripts\autogenerated_parts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DDF676-A33C-4DE0-AF9F-304D4D8A8246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745E2932-C0A4-45A5-B308-330E86B3210D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="23232" windowHeight="18576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="34500" windowHeight="13560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="capacitor" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17543" uniqueCount="2325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17552" uniqueCount="2327">
   <si>
     <t>Manufacturer</t>
   </si>
@@ -7018,6 +7018,12 @@
   </si>
   <si>
     <t>https://pim.murata.com/en-eu/pim/details/?partNum=GRM21BR61A476ME15L</t>
+  </si>
+  <si>
+    <t>GRM31CR61A107MEA8</t>
+  </si>
+  <si>
+    <t>https://pim.murata.com/en-eu/pim/details/?productCategoryId=ceramicCapacitorSMD&amp;partNum=GRM31CR61A107MEA8%23</t>
   </si>
 </sst>
 </file>
@@ -7364,7 +7370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{843D31F6-53B3-4092-975A-990A26A0450A}">
-  <dimension ref="A1:L1161"/>
+  <dimension ref="A1:L1162"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.21875" customWidth="1"/>
@@ -49840,6 +49846,41 @@
         <v>60</v>
       </c>
       <c r="L1161" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B1162" s="1" t="s">
+        <v>2325</v>
+      </c>
+      <c r="C1162" t="s">
+        <v>347</v>
+      </c>
+      <c r="D1162" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E1162" s="1">
+        <v>1206</v>
+      </c>
+      <c r="F1162" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1162" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="H1162" s="8" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I1162" t="s">
+        <v>2326</v>
+      </c>
+      <c r="J1162" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="K1162" t="s">
+        <v>60</v>
+      </c>
+      <c r="L1162" t="s">
         <v>43</v>
       </c>
     </row>
